--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99118</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99118</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>99376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>99376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1886,6 +1886,134 @@
       <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/131472489</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137221963</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99376</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rävamossen S, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>473179</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6417067</v>
+      </c>
+      <c r="S11" t="n">
+        <v>51</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Haurida</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>F-Ane-0024</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ingela Carlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>William Rosén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137221963</t>
         </is>
       </c>
     </row>
@@ -1900,6 +2028,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1143,11 +1143,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1274,11 +1270,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1405,11 +1397,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1536,11 +1524,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1667,11 +1651,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1798,11 +1778,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1929,11 +1905,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 60716-2025 artfynd.xlsx
+++ b/artfynd/A 60716-2025 artfynd.xlsx
@@ -1108,7 +1108,7 @@
         <v>131472289</v>
       </c>
       <c r="B5" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>131472298</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>131472381</v>
       </c>
       <c r="B7" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>131472400</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>131472457</v>
       </c>
       <c r="B9" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>131472489</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>137221963</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
